--- a/crates/xlstream-eval/tests/fixtures/text/case.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/text/case.xlsx
@@ -40,34 +40,34 @@
     <t xml:space="preserve">clean</t>
   </si>
   <si>
-    <t xml:space="preserve">hello</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WORLD</t>
+    <t xml:space="preserve">hello world</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABC DEF</t>
   </si>
   <si>
     <t xml:space="preserve">  spaces  here  </t>
   </si>
   <si>
-    <t xml:space="preserve">abc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">short</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test</t>
-  </si>
-  <si>
     <t xml:space="preserve">ProPer Case</t>
   </si>
   <si>
-    <t xml:space="preserve">num123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foo bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x</t>
+    <t xml:space="preserve">123abc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL CAPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  leading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trailing  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MiXeD CaSe</t>
   </si>
 </sst>
 </file>
@@ -369,23 +369,23 @@
       </c>
       <c r="B2" s="0" t="str">
         <f aca="false">UPPER(A2)</f>
-        <v>HELLO</v>
+        <v>HELLO WORLD</v>
       </c>
       <c r="C2" s="0" t="str">
         <f aca="false">LOWER(A2)</f>
-        <v>hello</v>
+        <v>hello world</v>
       </c>
       <c r="D2" s="0" t="str">
         <f aca="false">PROPER(A2)</f>
-        <v>Hello</v>
+        <v>Hello World</v>
       </c>
       <c r="E2" s="0" t="str">
         <f aca="false">TRIM(A2)</f>
-        <v>hello</v>
+        <v>hello world</v>
       </c>
       <c r="F2" s="0" t="str">
         <f aca="false">CLEAN(A2)</f>
-        <v>hello</v>
+        <v>hello world</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -394,23 +394,23 @@
       </c>
       <c r="B3" s="0" t="str">
         <f aca="false">UPPER(A3)</f>
-        <v>WORLD</v>
+        <v>ABC DEF</v>
       </c>
       <c r="C3" s="0" t="str">
         <f aca="false">LOWER(A3)</f>
-        <v>world</v>
+        <v>abc def</v>
       </c>
       <c r="D3" s="0" t="str">
         <f aca="false">PROPER(A3)</f>
-        <v>World</v>
+        <v>Abc Def</v>
       </c>
       <c r="E3" s="0" t="str">
         <f aca="false">TRIM(A3)</f>
-        <v>WORLD</v>
+        <v>ABC DEF</v>
       </c>
       <c r="F3" s="0" t="str">
         <f aca="false">CLEAN(A3)</f>
-        <v>WORLD</v>
+        <v>ABC DEF</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -444,23 +444,23 @@
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">UPPER(A5)</f>
-        <v>ABC</v>
+        <v>PROPER CASE</v>
       </c>
       <c r="C5" s="0" t="str">
         <f aca="false">LOWER(A5)</f>
-        <v>abc</v>
+        <v>proper case</v>
       </c>
       <c r="D5" s="0" t="str">
         <f aca="false">PROPER(A5)</f>
-        <v>Abc</v>
+        <v>Proper Case</v>
       </c>
       <c r="E5" s="0" t="str">
         <f aca="false">TRIM(A5)</f>
-        <v>abc</v>
+        <v>ProPer Case</v>
       </c>
       <c r="F5" s="0" t="str">
         <f aca="false">CLEAN(A5)</f>
-        <v>abc</v>
+        <v>ProPer Case</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -469,23 +469,23 @@
       </c>
       <c r="B6" s="0" t="str">
         <f aca="false">UPPER(A6)</f>
-        <v>SHORT</v>
+        <v>123ABC</v>
       </c>
       <c r="C6" s="0" t="str">
         <f aca="false">LOWER(A6)</f>
-        <v>short</v>
+        <v>123abc</v>
       </c>
       <c r="D6" s="0" t="str">
         <f aca="false">PROPER(A6)</f>
-        <v>Short</v>
+        <v>123Abc</v>
       </c>
       <c r="E6" s="0" t="str">
         <f aca="false">TRIM(A6)</f>
-        <v>short</v>
+        <v>123abc</v>
       </c>
       <c r="F6" s="0" t="str">
         <f aca="false">CLEAN(A6)</f>
-        <v>short</v>
+        <v>123abc</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -494,23 +494,23 @@
       </c>
       <c r="B7" s="0" t="str">
         <f aca="false">UPPER(A7)</f>
-        <v>TEST</v>
+        <v>ALL CAPS</v>
       </c>
       <c r="C7" s="0" t="str">
         <f aca="false">LOWER(A7)</f>
-        <v>test</v>
+        <v>all caps</v>
       </c>
       <c r="D7" s="0" t="str">
         <f aca="false">PROPER(A7)</f>
-        <v>Test</v>
+        <v>All Caps</v>
       </c>
       <c r="E7" s="0" t="str">
         <f aca="false">TRIM(A7)</f>
-        <v>test</v>
+        <v>ALL CAPS</v>
       </c>
       <c r="F7" s="0" t="str">
         <f aca="false">CLEAN(A7)</f>
-        <v>test</v>
+        <v>ALL CAPS</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -519,23 +519,23 @@
       </c>
       <c r="B8" s="0" t="str">
         <f aca="false">UPPER(A8)</f>
-        <v>PROPER CASE</v>
+        <v>NO CHANGE</v>
       </c>
       <c r="C8" s="0" t="str">
         <f aca="false">LOWER(A8)</f>
-        <v>proper case</v>
+        <v>no change</v>
       </c>
       <c r="D8" s="0" t="str">
         <f aca="false">PROPER(A8)</f>
-        <v>Proper Case</v>
+        <v>No Change</v>
       </c>
       <c r="E8" s="0" t="str">
         <f aca="false">TRIM(A8)</f>
-        <v>ProPer Case</v>
+        <v>no change</v>
       </c>
       <c r="F8" s="0" t="str">
         <f aca="false">CLEAN(A8)</f>
-        <v>ProPer Case</v>
+        <v>no change</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -544,23 +544,23 @@
       </c>
       <c r="B9" s="0" t="str">
         <f aca="false">UPPER(A9)</f>
-        <v>NUM123</v>
+        <v>  LEADING</v>
       </c>
       <c r="C9" s="0" t="str">
         <f aca="false">LOWER(A9)</f>
-        <v>num123</v>
+        <v>  leading</v>
       </c>
       <c r="D9" s="0" t="str">
         <f aca="false">PROPER(A9)</f>
-        <v>Num123</v>
+        <v>  Leading</v>
       </c>
       <c r="E9" s="0" t="str">
         <f aca="false">TRIM(A9)</f>
-        <v>num123</v>
+        <v>leading</v>
       </c>
       <c r="F9" s="0" t="str">
         <f aca="false">CLEAN(A9)</f>
-        <v>num123</v>
+        <v>  leading</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -569,23 +569,23 @@
       </c>
       <c r="B10" s="0" t="str">
         <f aca="false">UPPER(A10)</f>
-        <v>FOO BAR</v>
+        <v>TRAILING  </v>
       </c>
       <c r="C10" s="0" t="str">
         <f aca="false">LOWER(A10)</f>
-        <v>foo bar</v>
+        <v>trailing  </v>
       </c>
       <c r="D10" s="0" t="str">
         <f aca="false">PROPER(A10)</f>
-        <v>Foo Bar</v>
+        <v>Trailing  </v>
       </c>
       <c r="E10" s="0" t="str">
         <f aca="false">TRIM(A10)</f>
-        <v>foo bar</v>
+        <v>trailing</v>
       </c>
       <c r="F10" s="0" t="str">
         <f aca="false">CLEAN(A10)</f>
-        <v>foo bar</v>
+        <v>trailing  </v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -594,23 +594,23 @@
       </c>
       <c r="B11" s="0" t="str">
         <f aca="false">UPPER(A11)</f>
-        <v>X</v>
+        <v>MIXED CASE</v>
       </c>
       <c r="C11" s="0" t="str">
         <f aca="false">LOWER(A11)</f>
-        <v>x</v>
+        <v>mixed case</v>
       </c>
       <c r="D11" s="0" t="str">
         <f aca="false">PROPER(A11)</f>
-        <v>X</v>
+        <v>Mixed Case</v>
       </c>
       <c r="E11" s="0" t="str">
         <f aca="false">TRIM(A11)</f>
-        <v>x</v>
+        <v>MiXeD CaSe</v>
       </c>
       <c r="F11" s="0" t="str">
         <f aca="false">CLEAN(A11)</f>
-        <v>x</v>
+        <v>MiXeD CaSe</v>
       </c>
     </row>
   </sheetData>
